--- a/Excel/LegacyMonsterConfig.xlsx
+++ b/Excel/LegacyMonsterConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -41,70 +41,76 @@
     <t>Role</t>
   </si>
   <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>EndLevel</t>
+  </si>
+  <si>
+    <t>Atk</t>
+  </si>
+  <si>
+    <t>AtkRise</t>
+  </si>
+  <si>
+    <t>Def</t>
+  </si>
+  <si>
+    <t>DefRise</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HpRise</t>
+  </si>
+  <si>
+    <t>LegacyResist</t>
+  </si>
+  <si>
+    <t>LegacyRise</t>
+  </si>
+  <si>
+    <t>SkillIdList</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
     <t>Attr</t>
   </si>
   <si>
-    <t>RiseAttr</t>
-  </si>
-  <si>
-    <t>Def</t>
-  </si>
-  <si>
-    <t>RiseDef</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>RiseHp</t>
-  </si>
-  <si>
-    <t>SkillIdList</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>int[]</t>
   </si>
   <si>
-    <t>圣战</t>
-  </si>
-  <si>
-    <t>10000000</t>
-  </si>
-  <si>
-    <t>100000000000000</t>
-  </si>
-  <si>
-    <t>法神</t>
-  </si>
-  <si>
-    <t>1000000000</t>
-  </si>
-  <si>
-    <t>2000000000</t>
-  </si>
-  <si>
-    <t>20000000000000000</t>
-  </si>
-  <si>
-    <t>天尊</t>
-  </si>
-  <si>
-    <t>100000000000</t>
-  </si>
-  <si>
-    <t>400000000000</t>
-  </si>
-  <si>
-    <t>4000000000000000000</t>
+    <t>传世圣战</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>传世法神</t>
+  </si>
+  <si>
+    <t>传世天尊</t>
+  </si>
+  <si>
+    <t>3600000</t>
   </si>
 </sst>
 </file>
@@ -738,13 +744,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -752,11 +761,17 @@
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1079,61 +1094,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="23" style="3" customWidth="1"/>
-    <col min="11" max="11" width="21.75" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="8.91666666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.0833333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.5833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12.8333333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.0833333333333" style="4" customWidth="1"/>
+    <col min="16" max="16" width="15.8333333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -1142,34 +1164,46 @@
       <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -1178,282 +1212,356 @@
       <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
+        <v>16</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:18">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7">
+        <v>20</v>
+      </c>
+      <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-    </row>
-    <row r="7" customHeight="1" spans="3:14">
+      <c r="F6" s="9">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9">
+        <v>10</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="9">
+        <v>100</v>
+      </c>
+      <c r="O6" s="9">
+        <v>100</v>
+      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-    </row>
-    <row r="8" customHeight="1" spans="3:14">
+      <c r="F7" s="9">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9">
+        <v>10</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="9">
+        <v>100</v>
+      </c>
+      <c r="O7" s="9">
+        <v>100</v>
+      </c>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-    </row>
-    <row r="9" customHeight="1" spans="6:14">
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" customHeight="1" spans="6:14">
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" customHeight="1" spans="6:14">
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-    </row>
-    <row r="12" customHeight="1" spans="6:14">
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" customHeight="1" spans="6:14">
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" customHeight="1" spans="6:14">
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" customHeight="1" spans="6:14">
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="23" customHeight="1" spans="6:6">
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" customHeight="1" spans="6:6">
-      <c r="F24" s="8"/>
-    </row>
-    <row r="27" customHeight="1" spans="8:9">
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" customHeight="1" spans="8:9">
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" customHeight="1" spans="8:9">
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" customHeight="1" spans="8:9">
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" customHeight="1" spans="8:9">
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" customHeight="1" spans="8:9">
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" customHeight="1" spans="8:9">
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="34" customHeight="1" spans="8:9">
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-    </row>
-    <row r="35" customHeight="1" spans="8:9">
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-    </row>
-    <row r="36" customHeight="1" spans="8:9">
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="F8" s="9">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9">
+        <v>10</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="9">
+        <v>100</v>
+      </c>
+      <c r="O8" s="9">
+        <v>100</v>
+      </c>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:18">
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:18">
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:18">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:18">
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:18">
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:18">
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:18">
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+    </row>
+    <row r="23" customHeight="1" spans="8:11">
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" customHeight="1" spans="8:11">
+      <c r="H24" s="10"/>
+    </row>
+    <row r="27" customHeight="1" spans="8:11">
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" customHeight="1" spans="8:11">
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" customHeight="1" spans="8:11">
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" customHeight="1" spans="8:11">
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+    </row>
+    <row r="31" customHeight="1" spans="8:11">
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" customHeight="1" spans="8:11">
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+    </row>
+    <row r="33" customHeight="1" spans="10:11">
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+    </row>
+    <row r="34" customHeight="1" spans="10:11">
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+    </row>
+    <row r="35" customHeight="1" spans="10:11">
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+    </row>
+    <row r="36" customHeight="1" spans="10:11">
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 K3 L3 D4 E4 F4 G4 H4 I4 J4 K4 L4 C5 D5 E5 F5 G5 H5 I5 J5 K5 L5 M5 N5 C3:C4 M3:M4 N3:N4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 H3:M3 N3 O3 P3:R3 C4:E4 F4 G4 H4 I4 J4 K4 L4 M4 N4 O4 P4:R4 C5:E5 F5 G5 H5:M5 N5 O5 P5:R5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/LegacyMonsterConfig.xlsx
+++ b/Excel/LegacyMonsterConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -74,6 +74,9 @@
     <t>SkillIdList</t>
   </si>
   <si>
+    <t>Gold</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -86,10 +89,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>int[]</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
   <si>
     <t>传世圣战</t>
@@ -1106,12 +1109,11 @@
     <col min="9" max="9" width="12.0833333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="15" style="3" customWidth="1"/>
     <col min="11" max="11" width="15.5833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12.8333333333333" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.5" style="3" customWidth="1"/>
+    <col min="12" max="13" width="12.8333333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="11.3333333333333" style="1" customWidth="1"/>
     <col min="15" max="15" width="13.0833333333333" style="4" customWidth="1"/>
-    <col min="16" max="16" width="15.8333333333333" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.3333333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.58333333333333" style="2" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
@@ -1191,14 +1193,16 @@
       <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6"/>
+      <c r="Q3" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="R3" s="6"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1213,7 +1217,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>6</v>
@@ -1239,55 +1243,59 @@
       <c r="P4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="6"/>
+      <c r="Q4" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="R4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="O5" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="P5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="6"/>
+      <c r="Q5" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="R5" s="6"/>
     </row>
     <row r="6" customHeight="1" spans="1:18">
@@ -1295,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
@@ -1307,31 +1315,33 @@
         <v>10</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N6" s="9">
         <v>100</v>
       </c>
       <c r="O6" s="9">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
+      <c r="Q6" s="11">
+        <v>1000</v>
+      </c>
       <c r="R6" s="11"/>
     </row>
     <row r="7" customHeight="1" spans="1:18">
@@ -1339,7 +1349,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1351,31 +1361,33 @@
         <v>10</v>
       </c>
       <c r="H7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="K7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="L7" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N7" s="9">
         <v>100</v>
       </c>
       <c r="O7" s="9">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
+      <c r="Q7" s="11">
+        <v>1000</v>
+      </c>
       <c r="R7" s="11"/>
     </row>
     <row r="8" customHeight="1" spans="1:18">
@@ -1383,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -1395,31 +1407,33 @@
         <v>10</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" s="9">
         <v>100</v>
       </c>
       <c r="O8" s="9">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
+      <c r="Q8" s="11">
+        <v>1000</v>
+      </c>
       <c r="R8" s="11"/>
     </row>
     <row r="9" customHeight="1" spans="1:18">
@@ -1429,7 +1443,6 @@
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
-      <c r="N9" s="1"/>
       <c r="O9" s="12"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
@@ -1442,7 +1455,6 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
-      <c r="N10" s="1"/>
       <c r="O10" s="12"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
@@ -1455,7 +1467,6 @@
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
-      <c r="N11" s="1"/>
       <c r="O11" s="12"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
@@ -1468,7 +1479,6 @@
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
-      <c r="N12" s="1"/>
       <c r="O12" s="12"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
@@ -1481,7 +1491,6 @@
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
-      <c r="N13" s="1"/>
       <c r="O13" s="12"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -1494,7 +1503,6 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="1"/>
       <c r="O14" s="12"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -1507,7 +1515,6 @@
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="1"/>
       <c r="O15" s="12"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -1561,7 +1568,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 H3:M3 N3 O3 P3:R3 C4:E4 F4 G4 H4 I4 J4 K4 L4 M4 N4 O4 P4:R4 C5:E5 F5 G5 H5:M5 N5 O5 P5:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:R3 C4:P4 Q4 R4 C5:N5 O5 P5:R5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
